--- a/generation_zy/hiwo-物料2-1.xlsx
+++ b/generation_zy/hiwo-物料2-1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="11775" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2340" yWindow="2340" windowWidth="21555" windowHeight="10650" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物料信息" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="9">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -50,145 +50,8 @@
     </font>
     <font>
       <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
       <charset val="134"/>
       <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -200,8 +63,29 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -222,192 +106,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -426,253 +130,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -680,69 +145,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1068,6 +489,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1719,9 +1141,9 @@
           <t>R12-A02-01</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>试剂-1</t>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -1747,9 +1169,9 @@
           <t>R12-A02-02</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>试剂-2</t>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -1775,9 +1197,9 @@
           <t>R12-A02-03</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>试剂-3</t>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -1803,9 +1225,9 @@
           <t>R12-A02-04</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>试剂-4</t>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -1831,9 +1253,9 @@
           <t>R12-A02-05</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>试剂-5</t>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -1859,9 +1281,9 @@
           <t>R12-A02-06</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>试剂-6</t>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -1887,9 +1309,9 @@
           <t>R12-A02-07</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>试剂-7</t>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -1915,9 +1337,9 @@
           <t>R12-A02-08</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>试剂-8</t>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -1943,9 +1365,9 @@
           <t>R12-A02-09</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>试剂-9</t>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>llwc1</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -1971,9 +1393,9 @@
           <t>R12-A02-10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>试剂-10</t>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>llwc1</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -1999,9 +1421,9 @@
           <t>R12-A02-11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>试剂-11</t>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>llwc</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -2027,9 +1449,9 @@
           <t>R12-A02-12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>BENZANILIDE</t>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>llwc</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -2055,9 +1477,9 @@
           <t>R8-A03-01</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>试剂-1</t>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -2083,9 +1505,9 @@
           <t>R8-A03-02</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>试剂-2</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -2111,9 +1533,9 @@
           <t>R8-A03-03</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>试剂-3</t>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -2139,9 +1561,9 @@
           <t>R8-A03-04</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>试剂-4</t>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -2167,9 +1589,9 @@
           <t>R8-A03-05</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>试剂-5</t>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -2195,9 +1617,9 @@
           <t>R8-A03-06</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>试剂-6</t>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -2223,9 +1645,9 @@
           <t>R8-A03-07</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>试剂-7</t>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -2251,9 +1673,9 @@
           <t>R8-A03-08</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>试剂-8</t>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
